--- a/data/trans_orig/P04B3_1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34405</t>
+          <t>34174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64391</t>
+          <t>63005</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55040</t>
+          <t>57095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75601</t>
+          <t>74969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110950</t>
+          <t>109716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29418</t>
+          <t>28792</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>226110</t>
+          <t>226619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258565</t>
+          <t>259641</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220268</t>
+          <t>219382</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>242691</t>
+          <t>241936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>454714</t>
+          <t>453852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>494307</t>
+          <t>494357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>21593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26421</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27473</t>
+          <t>26905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57624</t>
+          <t>56308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38786</t>
+          <t>39755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61103</t>
+          <t>62055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71992</t>
+          <t>72631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110526</t>
+          <t>111238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188313</t>
+          <t>189965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>247649</t>
+          <t>249694</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169605</t>
+          <t>169195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208157</t>
+          <t>208741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>373442</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>442997</t>
+          <t>447526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>225898</t>
+          <t>225077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>288060</t>
+          <t>285645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>242358</t>
+          <t>244452</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>283233</t>
+          <t>286279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>484067</t>
+          <t>481069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>554401</t>
+          <t>554859</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38214</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61768</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33032</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52902</t>
+          <t>52837</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76461</t>
+          <t>76731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109969</t>
+          <t>108639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31303</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51115</t>
+          <t>52083</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50883</t>
+          <t>50477</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>75429</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86884</t>
+          <t>86390</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119537</t>
+          <t>118619</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32171</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59416</t>
+          <t>58480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38238</t>
+          <t>39420</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60072</t>
+          <t>59556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89290</t>
+          <t>92847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163373</t>
+          <t>163121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199180</t>
+          <t>198676</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200559</t>
+          <t>199631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>230806</t>
+          <t>230337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374013</t>
+          <t>370711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419415</t>
+          <t>419113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25451</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50023</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45081</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246579</t>
+          <t>259099</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80398</t>
+          <t>79838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337749</t>
+          <t>317917</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32655</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60071</t>
+          <t>60488</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>59266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64762</t>
+          <t>63090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112279</t>
+          <t>111339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30381</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58786</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>30396</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69117</t>
+          <t>70710</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67468</t>
+          <t>66813</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120876</t>
+          <t>117343</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167664</t>
+          <t>165489</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210240</t>
+          <t>208382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171431</t>
+          <t>164726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>323744</t>
+          <t>323664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>331983</t>
+          <t>336793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>517543</t>
+          <t>516488</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44747</t>
+          <t>44985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51076</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>91087</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>116299</t>
+          <t>116599</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>137914</t>
+          <t>138660</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>199206</t>
+          <t>199155</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234348</t>
+          <t>234745</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324026</t>
+          <t>322573</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>370376</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34952</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>58715</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25121</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>66784</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93482</t>
+          <t>94197</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29177</t>
+          <t>28948</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52249</t>
+          <t>51573</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>27070</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>44959</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61132</t>
+          <t>59027</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>89937</t>
+          <t>90350</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21406</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38425</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26526</t>
+          <t>26354</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>44073</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>51845</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77022</t>
+          <t>78568</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>141477</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>170765</t>
+          <t>171540</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>140993</t>
+          <t>142735</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>165745</t>
+          <t>167421</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>290619</t>
+          <t>288699</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>329791</t>
+          <t>330503</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58626</t>
+          <t>58203</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>96784</t>
+          <t>97139</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>44519</t>
+          <t>44664</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>129229</t>
+          <t>132106</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>102008</t>
+          <t>110297</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>208458</t>
+          <t>207701</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>102284</t>
+          <t>103842</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>149907</t>
+          <t>150524</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>59568</t>
+          <t>58585</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>167463</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>154042</t>
+          <t>154262</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>298774</t>
+          <t>298026</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>121650</t>
+          <t>123701</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>172434</t>
+          <t>172005</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>78241</t>
+          <t>81358</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>228459</t>
+          <t>228390</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>193427</t>
+          <t>198556</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>373824</t>
+          <t>377615</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>247718</t>
+          <t>247639</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>306175</t>
+          <t>306585</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>333430</t>
+          <t>334179</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>658097</t>
+          <t>655980</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>612078</t>
+          <t>609224</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1012847</t>
+          <t>1017532</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>226233</t>
+          <t>243244</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>702431</t>
+          <t>703594</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>512877</t>
+          <t>512766</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>552163</t>
+          <t>553377</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>644482</t>
+          <t>640687</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1233875</t>
+          <t>1235659</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>32945</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>107858</t>
+          <t>109003</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>77416</t>
+          <t>77470</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>107251</t>
+          <t>108902</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>104035</t>
+          <t>107346</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>207009</t>
+          <t>205537</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24931</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>93315</t>
+          <t>94646</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>49180</t>
+          <t>48707</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>74429</t>
+          <t>72610</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>74705</t>
+          <t>77201</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>153022</t>
+          <t>154599</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>44003</t>
+          <t>44447</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>642886</t>
+          <t>641903</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>43021</t>
+          <t>42945</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>74790</t>
+          <t>75623</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>815645</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>604346</t>
+          <t>588431</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>851570</t>
+          <t>845529</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>728939</t>
+          <t>725657</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1027691</t>
+          <t>1024724</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1453880</t>
+          <t>1443795</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1823570</t>
+          <t>1813152</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>330629</t>
+          <t>322515</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>468030</t>
+          <t>467180</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>376428</t>
+          <t>375967</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>511697</t>
+          <t>506125</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>765267</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>952842</t>
+          <t>954378</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>444993</t>
+          <t>436694</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>630534</t>
+          <t>628065</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>443065</t>
+          <t>453259</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>599033</t>
+          <t>602186</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>960290</t>
+          <t>945840</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1197337</t>
+          <t>1201885</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1550481</t>
+          <t>1557268</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2082784</t>
+          <t>2111323</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1692402</t>
+          <t>1699710</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2175886</t>
+          <t>2208275</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3319354</t>
+          <t>3302257</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4013669</t>
+          <t>4029371</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47212</t>
+          <t>59198</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34174</t>
+          <t>46118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63005</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>63475</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35213</t>
+          <t>50977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57095</t>
+          <t>76435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>91436</t>
+          <t>122673</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>103492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109716</t>
+          <t>142720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -951,69 +951,69 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>26198</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12009</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7322</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>17987</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t>5,69%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9417</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5714</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14492</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>38</t>
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>28627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28792</t>
+          <t>39945</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>243891</t>
+          <t>234211</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>226619</t>
+          <t>217176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>259641</t>
+          <t>248031</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>232257</t>
+          <t>236496</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>219382</t>
+          <t>223084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241936</t>
+          <t>249716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>476147</t>
+          <t>470708</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>453852</t>
+          <t>449812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>494357</t>
+          <t>491297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21593</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26615</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>42294</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26905</t>
+          <t>28143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56308</t>
+          <t>58069</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>53794</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39755</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62055</t>
+          <t>67116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89543</t>
+          <t>96088</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72631</t>
+          <t>78386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111238</t>
+          <t>115594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>219542</t>
+          <t>225591</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189965</t>
+          <t>199654</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>249694</t>
+          <t>259168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>187804</t>
+          <t>200605</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169195</t>
+          <t>180029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208741</t>
+          <t>221587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>407346</t>
+          <t>426197</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373442</t>
+          <t>393129</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>447526</t>
+          <t>462350</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>254772</t>
+          <t>258069</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>225077</t>
+          <t>225688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285645</t>
+          <t>284224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>263855</t>
+          <t>278103</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>244452</t>
+          <t>257862</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>286279</t>
+          <t>299187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>518627</t>
+          <t>536172</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>481069</t>
+          <t>498892</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>554859</t>
+          <t>569955</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>49093</t>
+          <t>51744</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>39514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63255</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>44670</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52837</t>
+          <t>55842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>91566</t>
+          <t>96415</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>79842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108639</t>
+          <t>112713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39684</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52083</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62337</t>
+          <t>66010</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50477</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75429</t>
+          <t>79127</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>102021</t>
+          <t>107120</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86390</t>
+          <t>91337</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>118619</t>
+          <t>124619</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44879</t>
+          <t>42807</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33478</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58480</t>
+          <t>55651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39420</t>
+          <t>39239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74185</t>
+          <t>72797</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59556</t>
+          <t>59569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92847</t>
+          <t>88216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>181378</t>
+          <t>179353</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163121</t>
+          <t>164315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198676</t>
+          <t>196639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>215012</t>
+          <t>215711</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199631</t>
+          <t>199583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>230337</t>
+          <t>231259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>396389</t>
+          <t>395065</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370711</t>
+          <t>369841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419113</t>
+          <t>417446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>315034</t>
+          <t>315014</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>315034</t>
+          <t>315014</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>315034</t>
+          <t>315014</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>664161</t>
+          <t>671396</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>664161</t>
+          <t>671396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>664161</t>
+          <t>671396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,67 +2432,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51593</t>
+          <t>53402</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14,31%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>48306</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>38067</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>59940</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>11,47%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>111782</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>45122</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>259099</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>147640</t>
+          <t>85677</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79838</t>
+          <t>70180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>317917</t>
+          <t>103790</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45312</t>
+          <t>53043</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32813</t>
+          <t>37000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60488</t>
+          <t>68973</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>49251</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26616</t>
+          <t>39289</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59266</t>
+          <t>61600</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>89188</t>
+          <t>102294</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>63090</t>
+          <t>84797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111339</t>
+          <t>125446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43556</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>34862</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61152</t>
+          <t>65986</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51480</t>
+          <t>62374</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>50477</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70710</t>
+          <t>77144</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>95037</t>
+          <t>110069</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>66813</t>
+          <t>90934</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>117343</t>
+          <t>133365</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>187832</t>
+          <t>235036</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>165489</t>
+          <t>209267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208382</t>
+          <t>256430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>268417</t>
+          <t>261062</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164726</t>
+          <t>242896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>323664</t>
+          <t>277868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>456248</t>
+          <t>496099</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336793</t>
+          <t>464974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>516488</t>
+          <t>523475</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41931</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>41719</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53432</t>
+          <t>64757</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32517</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>74448</t>
+          <t>89980</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>76014</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91087</t>
+          <t>105274</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>17864</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>26257</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>128175</t>
+          <t>143365</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>116599</t>
+          <t>129606</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>138660</t>
+          <t>154091</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>213951</t>
+          <t>178250</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>199155</t>
+          <t>168348</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234745</t>
+          <t>186770</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>342127</t>
+          <t>321614</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>322573</t>
+          <t>306274</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>370376</t>
+          <t>337345</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,102 +3570,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>49182</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>57528</t>
+          <t>61004</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>22,54%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>35484</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>27377</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>45361</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>13,45%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>84666</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>71840</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>98907</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>13,44%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>33065</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>25584</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>42258</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>78730</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>66784</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>94197</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>38686</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>28899</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51573</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34745</t>
+          <t>36918</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27070</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44959</t>
+          <t>46254</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>73527</t>
+          <t>75604</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>59027</t>
+          <t>63297</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>90350</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>29672</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21406</t>
+          <t>21978</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>34675</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>27674</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44073</t>
+          <t>44685</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>63837</t>
+          <t>65135</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>51845</t>
+          <t>53677</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>78568</t>
+          <t>79835</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>156027</t>
+          <t>153167</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142507</t>
+          <t>138745</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>171540</t>
+          <t>168401</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>154571</t>
+          <t>155885</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>142735</t>
+          <t>143134</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>167421</t>
+          <t>168724</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>310598</t>
+          <t>309052</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>288699</t>
+          <t>290356</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>330503</t>
+          <t>328350</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>76077</t>
+          <t>89464</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58203</t>
+          <t>69923</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>97139</t>
+          <t>111473</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>94489</t>
+          <t>112737</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>44664</t>
+          <t>95724</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>132106</t>
+          <t>131811</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>170566</t>
+          <t>202200</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>110297</t>
+          <t>176340</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>207701</t>
+          <t>230600</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>124074</t>
+          <t>138539</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>103842</t>
+          <t>116925</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>150524</t>
+          <t>165574</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>121460</t>
+          <t>144558</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>58585</t>
+          <t>127353</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>167463</t>
+          <t>166425</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>245534</t>
+          <t>283097</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>154262</t>
+          <t>251967</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>298026</t>
+          <t>314170</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>146629</t>
+          <t>166392</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>123701</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>172005</t>
+          <t>193046</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>165835</t>
+          <t>199523</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>81358</t>
+          <t>179543</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>228390</t>
+          <t>225047</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>312464</t>
+          <t>365915</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>198556</t>
+          <t>331090</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>377615</t>
+          <t>403613</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>277170</t>
+          <t>322472</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>247639</t>
+          <t>293636</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>306585</t>
+          <t>353918</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>465475</t>
+          <t>313077</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>334179</t>
+          <t>285957</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>655980</t>
+          <t>339133</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>742645</t>
+          <t>635550</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>609224</t>
+          <t>596123</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1017532</t>
+          <t>675299</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623950</t>
+          <t>716866</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623950</t>
+          <t>716866</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623950</t>
+          <t>716866</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>847259</t>
+          <t>769896</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>847259</t>
+          <t>769896</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>847259</t>
+          <t>769896</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1471209</t>
+          <t>1486762</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1471209</t>
+          <t>1486762</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1471209</t>
+          <t>1486762</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>509193</t>
+          <t>597931</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>243244</t>
+          <t>568511</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>703594</t>
+          <t>621503</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>533303</t>
+          <t>614249</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>512766</t>
+          <t>589502</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>553377</t>
+          <t>636801</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1042497</t>
+          <t>1212180</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>640687</t>
+          <t>1175209</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1235659</t>
+          <t>1246581</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>75353</t>
+          <t>85416</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>32945</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>109003</t>
+          <t>105139</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>92532</t>
+          <t>106162</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>77470</t>
+          <t>89252</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>108902</t>
+          <t>124449</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>167885</t>
+          <t>191578</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>107346</t>
+          <t>167974</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>205537</t>
+          <t>218106</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>63424</t>
+          <t>72510</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>57704</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>94646</t>
+          <t>91730</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>59916</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>48707</t>
+          <t>56941</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>72610</t>
+          <t>86521</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>123340</t>
+          <t>142663</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>77201</t>
+          <t>120806</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>154599</t>
+          <t>165111</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -5047,67 +5047,67 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>280750</t>
+          <t>42216</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>44447</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>641903</t>
+          <t>59142</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>29234</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>52691</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>4,79%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>69,12%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>31821</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>23317</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>42945</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>312571</t>
+          <t>82007</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>75623</t>
+          <t>65160</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>815645</t>
+          <t>102092</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830356</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830356</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830356</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646293</t>
+          <t>1628428</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646293</t>
+          <t>1628428</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646293</t>
+          <t>1628428</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>771982</t>
+          <t>890893</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>588431</t>
+          <t>835357</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>845529</t>
+          <t>945890</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>864557</t>
+          <t>911808</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>725657</t>
+          <t>867532</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1024724</t>
+          <t>962139</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1636539</t>
+          <t>1802701</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1443795</t>
+          <t>1729854</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1813152</t>
+          <t>1877262</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>417364</t>
+          <t>467694</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>322515</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>467180</t>
+          <t>514399</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>456754</t>
+          <t>528624</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>375967</t>
+          <t>492896</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>506125</t>
+          <t>573172</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>874117</t>
+          <t>996318</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>765267</t>
+          <t>947408</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>954378</t>
+          <t>1055853</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>559132</t>
+          <t>602486</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>436694</t>
+          <t>553874</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>628065</t>
+          <t>654311</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>543285</t>
+          <t>614041</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>453259</t>
+          <t>575851</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>602186</t>
+          <t>651834</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1102417</t>
+          <t>1216527</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>945840</t>
+          <t>1154464</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1201885</t>
+          <t>1281494</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1709993</t>
+          <t>1567890</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1557268</t>
+          <t>1507148</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2111323</t>
+          <t>1640260</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1845359</t>
+          <t>1678376</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1699710</t>
+          <t>1618982</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2208275</t>
+          <t>1734949</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>46,48%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>3246266</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>3163163</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>3326446</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
           <t>45,81%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>59,52%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>4031</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>3555352</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>3302257</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>4029371</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>49,6%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
